--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488116_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488116_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.07</v>
+        <v>6.4838</v>
       </c>
       <c r="E2" t="n">
-        <v>4.0972</v>
+        <v>4.5671</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9728</v>
+        <v>1.9167</v>
       </c>
       <c r="G2" t="n">
         <v>6.2089</v>
@@ -610,13 +610,13 @@
         <v>1.3876</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2688</v>
+        <v>0.145</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.624</v>
+        <v>-0.1541</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3552</v>
+        <v>0.2991</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2666</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ CANTERO</t>
+          <t>D. GARCÍA GAZQUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7395</v>
+        <v>4.5267</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5577</v>
+        <v>4.5267</v>
       </c>
       <c r="F3" t="n">
-        <v>4.1818</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>1.3971</v>
+        <v>4.5267</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2574</v>
+        <v>1.5133</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1397</v>
+        <v>3.0133</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4852</v>
+        <v>4.5267</v>
       </c>
       <c r="K3" t="n">
-        <v>1.036</v>
+        <v>1.5133</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5508</v>
+        <v>3.0133</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9119</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2214</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6905</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9733</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5858</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9897</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>1.039</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>1.9507</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.0068</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. GARCÍA GAZQUEZ</t>
+          <t>G. LOPEZ TORRE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5267</v>
+        <v>3.5814</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5267</v>
+        <v>2.8405</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.7409</v>
       </c>
       <c r="G4" t="n">
-        <v>4.5267</v>
+        <v>4.4161</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5133</v>
+        <v>2.5487</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0133</v>
+        <v>1.8674</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5267</v>
+        <v>4.4589</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5133</v>
+        <v>2.6029</v>
       </c>
       <c r="L4" t="n">
-        <v>3.0133</v>
+        <v>1.856</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>-0.0428</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0.0542</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>0.0114</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.1893</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-0.48</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-0.6074000000000001</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.1275</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-1.5441</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-1.0109</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. LOPEZ TORRE</t>
+          <t>J. RODRIGUEZ CANTERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1749</v>
+        <v>2.8004</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5744</v>
+        <v>-0.3986</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6005</v>
+        <v>3.1991</v>
       </c>
       <c r="G5" t="n">
-        <v>4.4161</v>
+        <v>1.3971</v>
       </c>
       <c r="H5" t="n">
-        <v>2.5487</v>
+        <v>1.2574</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8674</v>
+        <v>0.1397</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4589</v>
+        <v>0.4852</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6029</v>
+        <v>1.036</v>
       </c>
       <c r="L5" t="n">
-        <v>1.856</v>
+        <v>-0.5508</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0428</v>
+        <v>0.9119</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0542</v>
+        <v>0.2214</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0114</v>
+        <v>0.6905</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1893</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9733</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8865</v>
+        <v>1.0507</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8736</v>
+        <v>0.0827</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0129</v>
+        <v>0.9679</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.5441</v>
+        <v>1.7403</v>
       </c>
       <c r="W5" t="n">
-        <v>-1.0109</v>
+        <v>2.0068</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5331</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.6774</v>
+        <v>2.5922</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9241</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7533</v>
+        <v>1.8095</v>
       </c>
       <c r="G6" t="n">
         <v>1.7796</v>
@@ -922,13 +922,13 @@
         <v>1.5858</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5697</v>
+        <v>0.4845</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0479</v>
+        <v>-0.0934</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5218</v>
+        <v>0.578</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2666</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.4965</v>
+        <v>2.5913</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4504</v>
+        <v>1.124</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0461</v>
+        <v>1.4673</v>
       </c>
       <c r="G7" t="n">
         <v>3.2582</v>
@@ -1000,13 +1000,13 @@
         <v>2.5769</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.7528</v>
+        <v>-0.658</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1855</v>
+        <v>-0.5119</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5673</v>
+        <v>-0.1461</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6036</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3875</v>
+        <v>0.3979</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4631</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8506</v>
+        <v>0.9629</v>
       </c>
       <c r="G8" t="n">
         <v>1.9229</v>
@@ -1078,13 +1078,13 @@
         <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>1.077</v>
+        <v>1.0875</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0479</v>
+        <v>-0.054</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0291</v>
+        <v>1.1414</v>
       </c>
       <c r="V8" t="n">
         <v>-2.4142</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0392</v>
+        <v>0.2998</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5271</v>
+        <v>-2.3004</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4879</v>
+        <v>2.6002</v>
       </c>
       <c r="G9" t="n">
         <v>-0.0517</v>
@@ -1156,13 +1156,13 @@
         <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1769</v>
+        <v>-0.8379</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1855</v>
+        <v>-0.9589</v>
       </c>
       <c r="U9" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9129</v>
+        <v>-1.7767</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7533</v>
+        <v>-2.589</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8403</v>
+        <v>0.8123</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3463</v>
@@ -1234,13 +1234,13 @@
         <v>1.784</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1435</v>
+        <v>-0.0073</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.444</v>
+        <v>-0.2798</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3005</v>
+        <v>0.2724</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2071</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.631</v>
+        <v>-2.214</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4577</v>
+        <v>-3.2934</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8267</v>
+        <v>1.0794</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0486</v>
@@ -1312,13 +1312,13 @@
         <v>0.9911</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5824</v>
+        <v>-1.1655</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1232</v>
+        <v>-0.9589</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4593</v>
+        <v>-0.2066</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.7367</v>
+        <v>-2.9061</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5991</v>
+        <v>-4.7404</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8624</v>
+        <v>1.8343</v>
       </c>
       <c r="G12" t="n">
         <v>1.1007</v>
@@ -1390,13 +1390,13 @@
         <v>2.7751</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4401</v>
+        <v>0.2707</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1393</v>
+        <v>-0.2806</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5794</v>
+        <v>0.5513</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0882</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>15.7527</v>
+        <v>16.3767</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6697999999999995</v>
+        <v>-0.04569999999999919</v>
       </c>
       <c r="F13" t="n">
-        <v>16.4224</v>
+        <v>16.4226</v>
       </c>
       <c r="G13" t="n">
         <v>21.1636</v>
@@ -1468,10 +1468,10 @@
         <v>17.8401</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7344000000000002</v>
+        <v>-0.1103000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.440300000000001</v>
+        <v>-3.8163</v>
       </c>
       <c r="U13" t="n">
         <v>3.7059</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. ESPINAL REYNOSO</t>
+          <t>U. GARCES BENITEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.871</v>
+        <v>1.3715</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7403</v>
+        <v>0.0029</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1308</v>
+        <v>1.3686</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.8667</v>
+        <v>0.1731</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.1274</v>
+        <v>-0.5424</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.7393</v>
+        <v>0.7154</v>
       </c>
       <c r="J14" t="n">
-        <v>1.5553</v>
+        <v>0.2818</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4672</v>
+        <v>0.1211</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0881</v>
+        <v>0.1607</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.422</v>
+        <v>-0.1087</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.5946</v>
+        <v>-0.6634</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8274</v>
+        <v>0.5547</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9911</v>
+        <v>1.3876</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.9733</v>
+        <v>1.3876</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9469</v>
+        <v>-0.1891</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1604</v>
+        <v>-0.2789</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7866</v>
+        <v>0.0898</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7997</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.0068</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>U. GARCES BENITEZ</t>
+          <t>J. MORALES MUÑOZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0202</v>
+        <v>0.9053</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4046</v>
+        <v>0.9053</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4248</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1731</v>
+        <v>0.9053</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5424</v>
+        <v>0.3027</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7154</v>
+        <v>0.6027</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2818</v>
+        <v>0.9053</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1211</v>
+        <v>0.3027</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1607</v>
+        <v>0.6027</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1087</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6634</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5547</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3876</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5404</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6864</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.146</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MORALES MUÑOZ</t>
+          <t>J. ESPINAL REYNOSO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9053</v>
+        <v>0.8270999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9053</v>
+        <v>1.3141</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.487</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9053</v>
+        <v>-1.8667</v>
       </c>
       <c r="H16" t="n">
-        <v>0.3027</v>
+        <v>-0.1274</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6027</v>
+        <v>-1.7393</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9053</v>
+        <v>1.5553</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3027</v>
+        <v>1.4672</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6027</v>
+        <v>0.0881</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-3.422</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.5946</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-1.8274</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.9911</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.9733</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.903</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>-0.2658</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.1688</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.7997</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.0068</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0002</v>
+        <v>-0.5271</v>
       </c>
       <c r="E17" t="n">
-        <v>0.244</v>
+        <v>-0.3672</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2442</v>
+        <v>-0.1599</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6047</v>
@@ -1780,13 +1780,13 @@
         <v>0.3964</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4658</v>
+        <v>0.9388</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9215</v>
+        <v>0.3103</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5443</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2666</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9822</v>
+        <v>-0.6931</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3829</v>
+        <v>0.7376</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5992</v>
+        <v>-1.4308</v>
       </c>
       <c r="G18" t="n">
         <v>0.1047</v>
@@ -1858,13 +1858,13 @@
         <v>2.5769</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.7855</v>
+        <v>-0.4964</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.0481</v>
+        <v>-0.9275</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2626</v>
+        <v>0.4311</v>
       </c>
       <c r="V18" t="n">
         <v>2.0772</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. MAERIEN</t>
+          <t>I. VIVERO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.216</v>
+        <v>-2.5964</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.8485</v>
+        <v>-3.4076</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6325</v>
+        <v>0.8112</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.7344</v>
+        <v>-3.5104</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.19</v>
+        <v>-2.0335</v>
       </c>
       <c r="I19" t="n">
-        <v>-2.5444</v>
+        <v>-1.477</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0207</v>
+        <v>-0.5504</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0089</v>
+        <v>-0.369</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.0296</v>
+        <v>-0.1814</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7137</v>
+        <v>-2.96</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1989</v>
+        <v>-1.6645</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5148</v>
+        <v>-1.2955</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3964</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5858</v>
+        <v>2.7751</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0257</v>
+        <v>0.2928</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1121</v>
+        <v>-0.6329</v>
       </c>
       <c r="U19" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.9257</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9405</v>
+        <v>1.8107</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2666</v>
+        <v>1.7403</v>
       </c>
       <c r="X19" t="n">
-        <v>0.674</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. VIVERO RODRIGUEZ</t>
+          <t>L. MAERIEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4041</v>
+        <v>-3.3283</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.0188</v>
+        <v>-3.8485</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6147</v>
+        <v>0.5202</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.5104</v>
+        <v>-2.7344</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.0335</v>
+        <v>-0.19</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.477</v>
+        <v>-2.5444</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5504</v>
+        <v>-1.0207</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.369</v>
+        <v>1.0089</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1814</v>
+        <v>-2.0296</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.96</v>
+        <v>-1.7137</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.6645</v>
+        <v>-1.1989</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2955</v>
+        <v>-0.5148</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1893</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.9645</v>
+        <v>-1.9822</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7751</v>
+        <v>1.5858</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.515</v>
+        <v>-1.138</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2442</v>
+        <v>-1.1121</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7292</v>
+        <v>-0.0259</v>
       </c>
       <c r="V20" t="n">
-        <v>1.8107</v>
+        <v>0.9405</v>
       </c>
       <c r="W20" t="n">
-        <v>1.7403</v>
+        <v>0.2666</v>
       </c>
       <c r="X20" t="n">
-        <v>0.0704</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.6283</v>
+        <v>-5.021</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.4693</v>
+        <v>-6.3675</v>
       </c>
       <c r="F21" t="n">
-        <v>0.8411</v>
+        <v>1.3465</v>
       </c>
       <c r="G21" t="n">
         <v>-6.9374</v>
@@ -2092,13 +2092,13 @@
         <v>1.9822</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2783</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2641</v>
+        <v>-0.1622</v>
       </c>
       <c r="U21" t="n">
-        <v>0.5424</v>
+        <v>1.0478</v>
       </c>
       <c r="V21" t="n">
         <v>2.0219</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.3185</v>
+        <v>-6.6907</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.1879</v>
+        <v>-5.3916</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1306</v>
+        <v>-1.2991</v>
       </c>
       <c r="G22" t="n">
         <v>-6.693</v>
@@ -2170,13 +2170,13 @@
         <v>1.1893</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.4625</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.433</v>
+        <v>-0.6367</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3427</v>
+        <v>0.1743</v>
       </c>
       <c r="V22" t="n">
         <v>0.2666</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-15.7528</v>
+        <v>-15.7527</v>
       </c>
       <c r="E23" t="n">
-        <v>-16.4224</v>
+        <v>-16.4225</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6698999999999999</v>
+        <v>0.6697000000000002</v>
       </c>
       <c r="G23" t="n">
         <v>-21.1635</v>
@@ -2233,7 +2233,7 @@
         <v>-18.1191</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.9818</v>
+        <v>-8.981800000000002</v>
       </c>
       <c r="O23" t="n">
         <v>-9.1371</v>
@@ -2248,13 +2248,13 @@
         <v>14.8666</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7340999999999998</v>
+        <v>0.7342000000000003</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.706</v>
+        <v>-3.7058</v>
       </c>
       <c r="U23" t="n">
-        <v>4.4403</v>
+        <v>4.4401</v>
       </c>
       <c r="V23" t="n">
         <v>7.650000000000001</v>
@@ -2263,7 +2263,7 @@
         <v>8.168200000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5181000000000001</v>
+        <v>-0.5181000000000002</v>
       </c>
     </row>
   </sheetData>
